--- a/src/mirror/sensor_KP/mirror2_data/sensor_data.xlsx
+++ b/src/mirror/sensor_KP/mirror2_data/sensor_data.xlsx
@@ -2,28 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet name="Sensor Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="171027" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <color rgb="FF333333"/>
-      <sz val="9"/>
     </font>
     <font>
       <color rgb="00333333"/>
@@ -50,19 +50,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -140,7 +137,7 @@
     <from>
       <col>7</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1143000" cy="571500"/>
@@ -239,7 +236,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -274,7 +270,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -309,16 +304,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -440,46 +439,7 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -490,12 +450,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="13.57142857142857" customWidth="1" min="1" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="13.57142857142857" customWidth="1" min="9" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -558,196 +516,629 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260807_102630</t>
+          <t>20260807_162142</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>192.168.0.101: 4</t>
+          <t>192.168.0.134: 4</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>200N</t>
+          <t>100N</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[-150N, 150N]</t>
+          <t>[-60N, 60N]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[0, -160000, -5000]</t>
+          <t>[0, -120000, -5000]</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>motor9_data_20260807_102630_拟合图</t>
+          <t>motor4_data_20260807_162142_拟合图</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>y = 4052.9255x + 5219.0945</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>4052.9255</v>
+          <t>y = 51449.7611x + -8794.2262</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>51449.7611</t>
+        </is>
       </c>
     </row>
     <row r="3" ht="90" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260807_103329</t>
+          <t>20260807_162529</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>192.168.0.101: 4</t>
+          <t>192.168.0.134: 4</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>200N</t>
+          <t>100N</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[-150N, 150N]</t>
+          <t>[-60N, 60N]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[0, -160000, -5000]</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>motor9_data_20260807_103329_拟合图</t>
+          <t>[0, -120000, -5000]</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>motor4_data_20260807_162529_拟合图</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>y = 3990.8270x + 5544.4577</t>
+          <t>y = 51812.2972x + -5450.2298</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3990.8270</t>
+          <t>51812.2972</t>
         </is>
       </c>
     </row>
     <row r="4" ht="90" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260807_104122</t>
+          <t>20260807_162837</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>192.168.0.101: 4</t>
+          <t>192.168.0.134: 4</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>200N</t>
+          <t>100N</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[-150N, 150N]</t>
+          <t>[-60N, 60N]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[0, -160000, -5000]</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>motor9_data_20260807_104122_拟合图</t>
+          <t>[0, -120000, -5000]</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>motor4_data_20260807_162837_拟合图</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>y = 4051.7697x + 5006.5407</t>
+          <t>y = 15139.9341x + -3759.5423</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4051.7697</t>
+          <t>15139.9341</t>
         </is>
       </c>
     </row>
     <row r="5" ht="90" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260807_114019</t>
+          <t>20260807_163212</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>192.168.0.134: 4</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>100N</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>[-60N, 60N]</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>[0, -120000, -5000]</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>motor4_data_20260807_163212_拟合图</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>y = 14556.4011x + -1421.4648</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>14556.4011</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260807_163545</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>192.168.0.134: 4</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>100N</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>[-60N, 60N]</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>[0, -120000, -5000]</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>motor4_data_20260807_163545_拟合图</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>y = 14498.4483x + 723.3516</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>14498.4483</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260807_154907</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>192.168.0.134: 5</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>200N</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>[-150N, 150N]</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>[0, -160000, -5000]</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>motor5_data_20260807_154907_拟合图</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>y = 6472.6053x + -9038.0404</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6472.6053</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260807_155200</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>192.168.0.134: 5</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>200N</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>[-150N, 150N]</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>[0, -160000, -5000]</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>motor5_data_20260807_155200_拟合图</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>y = 4307.6808x + -5762.3073</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4307.6808</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260807_155427</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>192.168.0.134: 5</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>200N</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>[-150N, 150N]</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>[0, -160000, -5000]</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>motor5_data_20260807_155427_拟合图</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>y = 4165.0854x + -4016.1794</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4165.0854</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260807_155746</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>192.168.0.134: 5</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>200N</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[-150N, 150N]</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>[0, -160000, -5000]</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>motor5_data_20260807_155746_拟合图</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>y = 4173.7098x + -2241.4920</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4173.7098</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260807_160035</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>192.168.0.134: 5</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>200N</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>[-150N, 150N]</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>[0, -160000, -5000]</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>motor5_data_20260807_160035_拟合图</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>y = 4162.2474x + -207.0665</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4162.2474</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260807_161728</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>192.168.0.134: 5</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>200N</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[-150N, 150N]</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>[0, -160000, -5000]</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t>motor5_data_20260807_161728_拟合图</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>y = 4158.9125x + 1894.6662</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4158.9125</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260807_140259</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>9</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>192.168.0.101: 4</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D13" t="n">
         <v>9</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>200N</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>[-150N, 150N]</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>[0, -160000, -5000]</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>motor9_data_20260807_114019_拟合图</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>y = 4053.9887x + 6871.3460</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>4053.9887</t>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>motor9_data_20260807_140259_拟合图</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>y = -13923.9654x + -574207.9641</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-13923.9654</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260807_140519</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>192.168.0.101: 4</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>200N</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>[-150N, 150N]</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>[0, -160000, -5000]</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>motor9_data_20260807_140519_拟合图</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>y = 13064.6408x + 16747.8701</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>13064.6408</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/mirror/sensor_KP/mirror2_data/sensor_data.xlsx
+++ b/src/mirror/sensor_KP/mirror2_data/sensor_data.xlsx
@@ -17,13 +17,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <color rgb="00333333"/>
@@ -50,9 +54,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -129,36 +136,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>13</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1143000" cy="571500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -450,64 +427,64 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>测试时间</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>电机id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>传感器id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>弹簧id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>传感器量程</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>测试区间</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>脉冲范围</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>拟合图</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>线性方程</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>线性度</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>平均线性度</t>
         </is>
@@ -516,259 +493,249 @@
     <row r="2" ht="90" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260807_162142</t>
+          <t>20260729_144540</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>192.168.0.134: 4</t>
+          <t>192.168.0.100:1</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>100N</t>
+          <t>200N</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[-60N, 60N]</t>
+          <t>[-150N, 150N]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[0, -120000, -5000]</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>motor4_data_20260807_162142_拟合图</t>
+          <t>[0, -20W, -5K]</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>motor1_data_20260729_144540_拟合图</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>y = 51449.7611x + -8794.2262</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>51449.7611</t>
-        </is>
+          <t>y=4008x+1</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>4008</v>
       </c>
     </row>
     <row r="3" ht="90" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260807_162529</t>
+          <t>20260729_144540</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>192.168.0.134: 4</t>
+          <t>192.168.0.100:1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>100N</t>
+          <t>200N</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[-60N, 60N]</t>
+          <t>[-150N, 150N]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[0, -120000, -5000]</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>motor4_data_20260807_162529_拟合图</t>
+          <t>[0, -20W, -5K]</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>motor1_data_20260729_144540_拟合图</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>y = 51812.2972x + -5450.2298</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>51812.2972</t>
-        </is>
+          <t>y=4008x+1</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>4008</v>
       </c>
     </row>
     <row r="4" ht="90" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260807_162837</t>
+          <t>20260729_144540</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>192.168.0.134: 4</t>
+          <t>192.168.0.100:1</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>100N</t>
+          <t>200N</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[-60N, 60N]</t>
+          <t>[-150N, 150N]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[0, -120000, -5000]</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="inlineStr">
-        <is>
-          <t>motor4_data_20260807_162837_拟合图</t>
+          <t>[0, -20W, -5K]</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>motor1_data_20260729_144540_拟合图</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>y = 15139.9341x + -3759.5423</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>15139.9341</t>
-        </is>
+          <t>y=4008x+1</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>4008</v>
       </c>
     </row>
     <row r="5" ht="90" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260807_163212</t>
+          <t>20260729_144540</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>192.168.0.134: 4</t>
+          <t>192.168.0.100:1</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>100N</t>
+          <t>200N</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[-60N, 60N]</t>
+          <t>[-150N, 150N]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[0, -120000, -5000]</t>
-        </is>
-      </c>
-      <c r="H5" s="1" t="inlineStr">
-        <is>
-          <t>motor4_data_20260807_163212_拟合图</t>
+          <t>[0, -20W, -5K]</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>motor1_data_20260729_144540_拟合图</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>y = 14556.4011x + -1421.4648</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>14556.4011</t>
-        </is>
+          <t>y=4008x+1</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>4008</v>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260807_163545</t>
+          <t>20260729_153223</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>192.168.0.134: 4</t>
+          <t>192.168.0.100:1</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>100N</t>
+          <t>200N</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[-60N, 60N]</t>
+          <t>[-150N, 150N]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[0, -120000, -5000]</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="inlineStr">
-        <is>
-          <t>motor4_data_20260807_163545_拟合图</t>
+          <t>[0, -20W, -5K]</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>motor1_data_20260729_153223_拟合图</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>y = 14498.4483x + 723.3516</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>14498.4483</t>
-        </is>
+          <t>y=4009x+1</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>4009</v>
       </c>
     </row>
     <row r="7" ht="90" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260807_154907</t>
+          <t>20260729_153223</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>192.168.0.134: 5</t>
+          <t>192.168.0.100:1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -782,41 +749,39 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[0, -160000, -5000]</t>
-        </is>
-      </c>
-      <c r="H7" s="1" t="inlineStr">
-        <is>
-          <t>motor5_data_20260807_154907_拟合图</t>
+          <t>[0, -20W, -5K]</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>motor1_data_20260729_153223_拟合图</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>y = 6472.6053x + -9038.0404</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>6472.6053</t>
-        </is>
+          <t>y=4009x+1</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>4009</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260807_155200</t>
+          <t>20260729_153223</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>192.168.0.134: 5</t>
+          <t>192.168.0.100:1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -830,41 +795,39 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[0, -160000, -5000]</t>
-        </is>
-      </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t>motor5_data_20260807_155200_拟合图</t>
+          <t>[0, -20W, -5K]</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>motor1_data_20260729_153223_拟合图</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>y = 4307.6808x + -5762.3073</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>4307.6808</t>
-        </is>
+          <t>y=4009x+1</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>4009</v>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260807_155427</t>
+          <t>20260729_153223</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>192.168.0.134: 5</t>
+          <t>192.168.0.100:1</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -878,41 +841,39 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[0, -160000, -5000]</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
-          <t>motor5_data_20260807_155427_拟合图</t>
+          <t>[0, -20W, -5K]</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>motor1_data_20260729_153223_拟合图</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>y = 4165.0854x + -4016.1794</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>4165.0854</t>
-        </is>
+          <t>y=4009x+1</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>4009</v>
       </c>
     </row>
     <row r="10" ht="90" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260807_155746</t>
+          <t>20260729_154924</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>192.168.0.134: 5</t>
+          <t>192.168.0.100:1</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -926,41 +887,39 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[0, -160000, -5000]</t>
-        </is>
-      </c>
-      <c r="H10" s="1" t="inlineStr">
-        <is>
-          <t>motor5_data_20260807_155746_拟合图</t>
+          <t>[0, -20W, -5K]</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>motor1_data_20260729_154924_拟合图</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>y = 4173.7098x + -2241.4920</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4173.7098</t>
-        </is>
+          <t>y=4018x+1</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>4018</v>
       </c>
     </row>
     <row r="11" ht="90" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260807_160035</t>
+          <t>20260729_154924</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>192.168.0.134: 5</t>
+          <t>192.168.0.100:1</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -974,41 +933,39 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>[0, -160000, -5000]</t>
-        </is>
-      </c>
-      <c r="H11" s="1" t="inlineStr">
-        <is>
-          <t>motor5_data_20260807_160035_拟合图</t>
+          <t>[0, -20W, -5K]</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>motor1_data_20260729_154924_拟合图</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>y = 4162.2474x + -207.0665</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>4162.2474</t>
-        </is>
+          <t>y=4018x+1</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>4018</v>
       </c>
     </row>
     <row r="12" ht="90" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260807_161728</t>
+          <t>20260729_154924</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>192.168.0.134: 5</t>
+          <t>192.168.0.100:1</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1022,41 +979,39 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[0, -160000, -5000]</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="inlineStr">
-        <is>
-          <t>motor5_data_20260807_161728_拟合图</t>
+          <t>[0, -20W, -5K]</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>motor1_data_20260729_154924_拟合图</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>y = 4158.9125x + 1894.6662</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>4158.9125</t>
-        </is>
+          <t>y=4018x+1</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>4018</v>
       </c>
     </row>
     <row r="13" ht="90" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260807_140259</t>
+          <t>20260729_154924</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>192.168.0.101: 4</t>
+          <t>192.168.0.100:1</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1070,75 +1025,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>[0, -160000, -5000]</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="inlineStr">
-        <is>
-          <t>motor9_data_20260807_140259_拟合图</t>
+          <t>[0, -20W, -5K]</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>motor1_data_20260729_154924_拟合图</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>y = -13923.9654x + -574207.9641</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>-13923.9654</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>20260807_140519</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>9</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>192.168.0.101: 4</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>9</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>200N</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>[-150N, 150N]</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>[0, -160000, -5000]</t>
-        </is>
-      </c>
-      <c r="H14" s="1" t="inlineStr">
-        <is>
-          <t>motor9_data_20260807_140519_拟合图</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>y = 13064.6408x + 16747.8701</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>13064.6408</t>
-        </is>
+          <t>y=4018x+1</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>4018</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>